--- a/ios/Verification/office-layout/OfficeSampleTable.xlsx
+++ b/ios/Verification/office-layout/OfficeSampleTable.xlsx
@@ -464,7 +464,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">St.Catherine(세인트 캐서린)</t>
+          <t xml:space="preserve">St. Catherine(세인트 캐서린)</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">

--- a/ios/Verification/office-layout/OfficeSampleTable.xlsx
+++ b/ios/Verification/office-layout/OfficeSampleTable.xlsx
@@ -78,7 +78,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDE6E2"/>
+        <fgColor rgb="FFFBE6E2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -90,7 +90,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8DF71"/>
+        <fgColor rgb="FFF7DE72"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,7 +426,7 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.04" customWidth="1"/>
+    <col min="1" max="1" width="8.97" customWidth="1"/>
     <col min="2" max="2" width="22.79" customWidth="1"/>
     <col min="3" max="3" width="1.95" customWidth="1"/>
     <col min="4" max="4" width="30.70" customWidth="1"/>
@@ -454,7 +454,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.41.22. xx</t>
+          <t xml:space="preserve">10.41.22.xx</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="13.69" customHeight="1">
+    <row r="10" ht="13.91" customHeight="1">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="16.06" customHeight="1">
+    <row r="11" ht="15.84" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">USA1</t>

--- a/ios/Verification/office-layout/OfficeSampleTable.xlsx
+++ b/ios/Verification/office-layout/OfficeSampleTable.xlsx
@@ -9,11 +9,23 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -31,14 +43,12 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11.0"/>
       <color rgb="FF331E04"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11.0"/>
       <color rgb="FF332005"/>
       <name val="Arial"/>
@@ -290,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -307,6 +317,12 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -322,7 +338,10 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -334,7 +353,7 @@
     <xf numFmtId="49" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -409,7 +428,7 @@
     <xf numFmtId="49" fontId="2" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -630,12 +649,12 @@
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Shepherd(쉐퍼드)</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">MNY</t>
         </is>
@@ -647,17 +666,17 @@
       </c>
     </row>
     <row r="11" ht="15.84" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">USA1</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Oregon(오레곤)</t>
         </is>
       </c>
-      <c r="C11" s="7"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Bevorton(비버튼)</t>
@@ -675,9 +694,9 @@
       </c>
     </row>
     <row r="12" ht="14.97" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tigard(타이거드)</t>
@@ -695,18 +714,18 @@
       </c>
     </row>
     <row r="13" ht="15.11" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">USA2</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">Seattle(시애틀)</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="C13" s="11"/>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Lynwood Gmart</t>
         </is>
@@ -723,9 +742,9 @@
       </c>
     </row>
     <row r="14" ht="15.00" customHeight="1">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Bellevue(벨뷰)</t>
@@ -743,10 +762,10 @@
       </c>
     </row>
     <row r="15" ht="15.00" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Federal Way</t>
         </is>
@@ -763,10 +782,10 @@
       </c>
     </row>
     <row r="16" ht="15.04" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Lynwood</t>
         </is>
@@ -783,9 +802,9 @@
       </c>
     </row>
     <row r="17" ht="15.16" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Redmond(레드몬드)</t>
@@ -803,10 +822,10 @@
       </c>
     </row>
     <row r="18" ht="15.22" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Tacoma</t>
         </is>
@@ -823,10 +842,10 @@
       </c>
     </row>
     <row r="19" ht="15.45" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">UW</t>
         </is>
@@ -843,18 +862,18 @@
       </c>
     </row>
     <row r="20" ht="14.44" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">USA3</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Denver(덴버)</t>
         </is>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="C20" s="9"/>
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Westminster</t>
         </is>
@@ -871,10 +890,10 @@
       </c>
     </row>
     <row r="21" ht="14.92" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="A21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Aurora</t>
         </is>
@@ -891,16 +910,15 @@
       </c>
     </row>
     <row r="22" ht="16.71" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">USA4</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
-              <b/>
               <sz val="11.0"/>
               <color rgb="FF000000"/>
               <rFont val="Arial"/>
@@ -910,7 +928,6 @@
           </r>
           <r>
             <rPr>
-              <b/>
               <sz val="11.0"/>
               <color rgb="FF372509"/>
               <rFont val="Malgun Gothic"/>
@@ -920,7 +937,6 @@
           </r>
           <r>
             <rPr>
-              <b/>
               <sz val="11.0"/>
               <color rgb="FF352406"/>
               <rFont val="Arial"/>
@@ -930,34 +946,33 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="C22" s="15"/>
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">West Jordan</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">HWJ</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">10.21.86.xx</t>
         </is>
       </c>
     </row>
     <row r="23" ht="13.53" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">VAN</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <r>
             <rPr>
-              <b/>
               <sz val="11.0"/>
               <color rgb="FF000000"/>
               <rFont val="Arial"/>
@@ -967,7 +982,6 @@
           </r>
           <r>
             <rPr>
-              <b/>
               <sz val="11.0"/>
               <color rgb="FF0E1E3D"/>
               <rFont val="Arial"/>
@@ -977,7 +991,6 @@
           </r>
           <r>
             <rPr>
-              <b/>
               <sz val="11.0"/>
               <color rgb="FF000000"/>
               <rFont val="Malgun Gothic"/>
@@ -987,158 +1000,158 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="C23" s="20"/>
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">UBC</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">EUB</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">10.11.68.xx</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.38" customHeight="1">
-      <c r="A24" s="16"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="A24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Coquitlam</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">HCQ</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">10.11.0.xx</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14.75" customHeight="1">
-      <c r="A25" s="16"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="A25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">Dunbar</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">HDB</t>
         </is>
       </c>
-      <c r="F25" s="26" t="inlineStr">
+      <c r="F25" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">10.11.67.xx</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.30" customHeight="1">
-      <c r="A26" s="16"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">Downtown</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">HDN</t>
         </is>
       </c>
-      <c r="F26" s="28" t="inlineStr">
+      <c r="F26" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">192.168.10.xx</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.13" customHeight="1">
-      <c r="A27" s="16"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Langley</t>
         </is>
       </c>
-      <c r="E27" s="30" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">HLL</t>
         </is>
       </c>
-      <c r="F27" s="31" t="inlineStr">
+      <c r="F27" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">192.168.20.xx</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.32" customHeight="1">
-      <c r="A28" s="16"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="A28" s="19"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Port Coquitlam</t>
         </is>
       </c>
-      <c r="E28" s="33" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">HPC</t>
         </is>
       </c>
-      <c r="F28" s="34" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">10.11.66.xx</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.00" customHeight="1">
-      <c r="A29" s="16"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="35" t="inlineStr">
+      <c r="A29" s="19"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">Richmond</t>
         </is>
       </c>
-      <c r="E29" s="36" t="inlineStr">
+      <c r="E29" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">HRM</t>
         </is>
       </c>
-      <c r="F29" s="37" t="inlineStr">
+      <c r="F29" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">10.64.1.xx</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.37" customHeight="1">
-      <c r="A30" s="16"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="38" t="inlineStr">
+      <c r="A30" s="19"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">Victoria</t>
         </is>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">HVT</t>
         </is>
       </c>
-      <c r="F30" s="39" t="inlineStr">
+      <c r="F30" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">10.11.69.xx</t>
         </is>
@@ -1146,7 +1159,7 @@
     </row>
     <row r="31" ht="198.59" customHeight="1"/>
     <row r="32" ht="26.40" customHeight="1">
-      <c r="C32" s="40" t="inlineStr">
+      <c r="C32" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">point</t>
         </is>

--- a/ios/Verification/office-layout/OfficeSampleTable.xlsx
+++ b/ios/Verification/office-layout/OfficeSampleTable.xlsx
@@ -55,13 +55,13 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="22.0"/>
+      <sz val="16.4"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -70,205 +70,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE4EDFA"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3CF"/>
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBF8D2"/>
+        <fgColor rgb="FFFCE4D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBE6E2"/>
+        <fgColor rgb="FFEEF4F3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6DD"/>
+        <fgColor rgb="FFFFE699"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7DE72"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE476"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE97C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE678"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E275"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73B7F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76BAFB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC5FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FC1F6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82BEF6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84C7F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80C1F8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80BFF8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF89C5F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF85C1F7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83C1F8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FC2FA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83BFF6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC1FB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CBDF9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80BEF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FBFFA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CBAF9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7EBDF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80C1FB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FBDF8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7DBDF8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ABCFA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7EBCF6"/>
+        <fgColor rgb="FF9BC2E6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,132 +132,93 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="26" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="28" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="30" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="31" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="32" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="33" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="34" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -446,11 +239,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.97" customWidth="1"/>
-    <col min="2" max="2" width="22.79" customWidth="1"/>
-    <col min="3" max="3" width="1.95" customWidth="1"/>
-    <col min="4" max="4" width="30.70" customWidth="1"/>
-    <col min="5" max="5" width="9.32" customWidth="1"/>
-    <col min="6" max="6" width="17.77" customWidth="1"/>
+    <col min="2" max="2" width="25.46" customWidth="1"/>
+    <col min="3" max="3" width="30.70" customWidth="1"/>
+    <col min="4" max="4" width="9.32" customWidth="1"/>
+    <col min="5" max="5" width="17.77" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.56" customHeight="1">
@@ -460,18 +252,17 @@
         </is>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Decarie(데카리)</t>
         </is>
       </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HDC</t>
+        </is>
+      </c>
       <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HDC</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10.41.22.xx</t>
         </is>
@@ -480,18 +271,17 @@
     <row r="2" ht="17.00" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">St. Catherine(세인트 캐서린)</t>
         </is>
       </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSC</t>
+        </is>
+      </c>
       <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HSC</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10.41.23.xx</t>
         </is>
@@ -500,18 +290,17 @@
     <row r="3" ht="16.38" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">St.Jacques(생자크)</t>
         </is>
       </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSJ</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HSJ</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10.41.21.xx</t>
         </is>
@@ -528,18 +317,17 @@
           <t xml:space="preserve">Toronto(토론토)</t>
         </is>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Bloor(블루어)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">HBL</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10.31.46.xx</t>
         </is>
@@ -548,18 +336,17 @@
     <row r="5" ht="15.77" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Dundas(던다스)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">HDD</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10.31.47.xx</t>
         </is>
@@ -568,18 +355,17 @@
     <row r="6" ht="14.94" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Finch(핀치)</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">HFC</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10.31.42.xx</t>
         </is>
@@ -588,18 +374,17 @@
     <row r="7" ht="14.62" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">North York(노스 요크)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">HNY</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10.31.44.xx</t>
         </is>
@@ -608,18 +393,17 @@
     <row r="8" ht="14.86" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Richmond HII(리치몬드 힐)</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Richmond Hill(리치몬드 힐)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">HRH</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10.31.11.xx</t>
         </is>
@@ -628,18 +412,17 @@
     <row r="9" ht="15.08" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Steeles(스틸스)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">HSS</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">10.31.45.xx</t>
         </is>
@@ -648,274 +431,262 @@
     <row r="10" ht="13.91" customHeight="1">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Shepherd(쉐퍼드)</t>
         </is>
       </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MNY</t>
+        </is>
+      </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNY</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">10.31.43.xx</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15.84" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">USA1</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Oregon(오레곤)</t>
         </is>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Bevorton(비버튼)</t>
         </is>
       </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GBV</t>
+        </is>
+      </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GBV</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">10.54.1.xx</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14.97" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="A12" s="10"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tigard(타이거드)</t>
         </is>
       </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTG</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTG</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">10.51.1.xx</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15.11" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">USA2</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Seattle(시애틀)</t>
         </is>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Lynwood Gmart</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">GLW</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">10.59.1.xx</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.00" customHeight="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Bellevue(벨뷰)</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">HBE</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">10.81.1.xx</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.00" customHeight="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Federal Way</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">HFW</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">10.52.1.xx</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15.04" customHeight="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Lynwood</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">HLW</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">10.53.1.xx</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15.16" customHeight="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Redmond(레드몬드)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">HRD</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">10.51.85.xx</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15.22" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">Tacoma</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">HTM</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">10.57.1.xx</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15.45" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">UW</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">HUW</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">10.51.83.xx</t>
         </is>
       </c>
     </row>
     <row r="20" ht="14.44" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">USA3</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Denver(덴버)</t>
         </is>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Westminster</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">GWM</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">10.58.1.xx</t>
         </is>
       </c>
     </row>
     <row r="21" ht="14.92" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Aurora</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">HAR</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">10.55.1.xx</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16.71" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">USA4</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -946,30 +717,29 @@
           </r>
         </is>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">West Jordan</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">HWJ</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">10.21.86.xx</t>
         </is>
       </c>
     </row>
     <row r="23" ht="13.53" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">VAN</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1000,186 +770,177 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">UBC</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">EUB</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="E23" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">10.11.68.xx</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.38" customHeight="1">
-      <c r="A24" s="19"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Coquitlam</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">HCQ</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="E24" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">10.11.0.xx</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14.75" customHeight="1">
-      <c r="A25" s="19"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Dunbar</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="D25" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">HDB</t>
         </is>
       </c>
-      <c r="F25" s="29" t="inlineStr">
+      <c r="E25" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">10.11.67.xx</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.30" customHeight="1">
-      <c r="A26" s="19"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="30" t="inlineStr">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Downtown</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="D26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">HDN</t>
         </is>
       </c>
-      <c r="F26" s="31" t="inlineStr">
+      <c r="E26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">192.168.10.xx</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.13" customHeight="1">
-      <c r="A27" s="19"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Langley</t>
         </is>
       </c>
-      <c r="E27" s="33" t="inlineStr">
+      <c r="D27" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">HLL</t>
         </is>
       </c>
-      <c r="F27" s="34" t="inlineStr">
+      <c r="E27" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">192.168.20.xx</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.32" customHeight="1">
-      <c r="A28" s="19"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="35" t="inlineStr">
+      <c r="A28" s="26"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Port Coquitlam</t>
         </is>
       </c>
-      <c r="E28" s="36" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">HPC</t>
         </is>
       </c>
-      <c r="F28" s="37" t="inlineStr">
+      <c r="E28" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">10.11.66.xx</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.00" customHeight="1">
-      <c r="A29" s="19"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="38" t="inlineStr">
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Richmond</t>
         </is>
       </c>
-      <c r="E29" s="39" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">HRM</t>
         </is>
       </c>
-      <c r="F29" s="40" t="inlineStr">
+      <c r="E29" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">10.64.1.xx</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.37" customHeight="1">
-      <c r="A30" s="19"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="41" t="inlineStr">
+      <c r="A30" s="26"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Victoria</t>
         </is>
       </c>
-      <c r="E30" s="33" t="inlineStr">
+      <c r="D30" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">HVT</t>
         </is>
       </c>
-      <c r="F30" s="42" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">10.11.69.xx</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="198.59" customHeight="1"/>
-    <row r="32" ht="26.40" customHeight="1">
-      <c r="C32" s="43" t="inlineStr">
+    <row r="31" ht="201.93" customHeight="1"/>
+    <row r="32" ht="19.72" customHeight="1">
+      <c r="C32" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">point</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A1:C3"/>
+  <mergeCells count="12">
+    <mergeCell ref="A1:B3"/>
     <mergeCell ref="A4:A10"/>
-    <mergeCell ref="B4:C10"/>
+    <mergeCell ref="B4:B10"/>
     <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="A13:A19"/>
-    <mergeCell ref="B13:C19"/>
+    <mergeCell ref="B13:B19"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="A23:A30"/>
-    <mergeCell ref="B23:C30"/>
-    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="B23:B30"/>
+    <mergeCell ref="C32:E32"/>
   </mergeCells>
   <pageMargins left="0.72" right="0.79" top="0.92" bottom="0.3" header="0" footer="0"/>
   <pageSetup paperSize="1" orientation="portrait" fitToWidth="1" fitToHeight="0"/>

--- a/ios/Verification/office-layout/OfficeSampleTable.xlsx
+++ b/ios/Verification/office-layout/OfficeSampleTable.xlsx
@@ -88,7 +88,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEF4F3"/>
+        <fgColor rgb="FFEEF5F3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -135,91 +135,91 @@
   <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -245,7 +245,7 @@
     <col min="5" max="5" width="17.77" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.56" customHeight="1">
+    <row r="1" ht="16.79" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Montreal(몬트리올)</t>
@@ -268,7 +268,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="17.00" customHeight="1">
+    <row r="2" ht="16.86" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="inlineStr">
@@ -287,7 +287,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16.38" customHeight="1">
+    <row r="3" ht="16.41" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="inlineStr">
@@ -306,7 +306,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16.51" customHeight="1">
+    <row r="4" ht="16.62" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TOT</t>
@@ -333,7 +333,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.77" customHeight="1">
+    <row r="5" ht="15.74" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="inlineStr">
@@ -352,7 +352,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="14.94" customHeight="1">
+    <row r="6" ht="14.98" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
       <c r="C6" s="6" t="inlineStr">
@@ -447,7 +447,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15.84" customHeight="1">
+    <row r="11" ht="15.70" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">USA1</t>
@@ -474,7 +474,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="14.97" customHeight="1">
+    <row r="12" ht="14.54" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2" t="inlineStr">
@@ -520,7 +520,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15.00" customHeight="1">
+    <row r="14" ht="15.47" customHeight="1">
       <c r="A14" s="11"/>
       <c r="B14" s="12"/>
       <c r="C14" s="15" t="inlineStr">
@@ -539,7 +539,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15.00" customHeight="1">
+    <row r="15" ht="15.06" customHeight="1">
       <c r="A15" s="11"/>
       <c r="B15" s="12"/>
       <c r="C15" s="13" t="inlineStr">
@@ -558,7 +558,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15.04" customHeight="1">
+    <row r="16" ht="15.07" customHeight="1">
       <c r="A16" s="11"/>
       <c r="B16" s="12"/>
       <c r="C16" s="13" t="inlineStr">
@@ -577,7 +577,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.16" customHeight="1">
+    <row r="17" ht="15.15" customHeight="1">
       <c r="A17" s="11"/>
       <c r="B17" s="12"/>
       <c r="C17" s="15" t="inlineStr">
@@ -596,7 +596,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.22" customHeight="1">
+    <row r="18" ht="14.97" customHeight="1">
       <c r="A18" s="11"/>
       <c r="B18" s="12"/>
       <c r="C18" s="13" t="inlineStr">
@@ -615,7 +615,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.45" customHeight="1">
+    <row r="19" ht="15.79" customHeight="1">
       <c r="A19" s="11"/>
       <c r="B19" s="12"/>
       <c r="C19" s="16" t="inlineStr">
@@ -634,7 +634,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="14.44" customHeight="1">
+    <row r="20" ht="14.74" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">USA3</t>
@@ -661,7 +661,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="14.92" customHeight="1">
+    <row r="21" ht="15.09" customHeight="1">
       <c r="A21" s="17"/>
       <c r="B21" s="18"/>
       <c r="C21" s="19" t="inlineStr">
@@ -680,7 +680,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16.71" customHeight="1">
+    <row r="22" ht="16.01" customHeight="1">
       <c r="A22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">USA4</t>
@@ -733,7 +733,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="13.53" customHeight="1">
+    <row r="23" ht="13.86" customHeight="1">
       <c r="A23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">VAN</t>
@@ -786,7 +786,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.38" customHeight="1">
+    <row r="24" ht="15.37" customHeight="1">
       <c r="A24" s="26"/>
       <c r="B24" s="27"/>
       <c r="C24" s="28" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="14.75" customHeight="1">
+    <row r="25" ht="14.60" customHeight="1">
       <c r="A25" s="26"/>
       <c r="B25" s="27"/>
       <c r="C25" s="28" t="inlineStr">
@@ -900,7 +900,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15.37" customHeight="1">
+    <row r="30" ht="15.22" customHeight="1">
       <c r="A30" s="26"/>
       <c r="B30" s="27"/>
       <c r="C30" s="28" t="inlineStr">
@@ -919,7 +919,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="201.93" customHeight="1"/>
+    <row r="31" ht="202.09" customHeight="1"/>
     <row r="32" ht="19.72" customHeight="1">
       <c r="C32" s="30" t="inlineStr">
         <is>
